--- a/Boards/GPS-Speedsurfing-Board-Stats.xlsx
+++ b/Boards/GPS-Speedsurfing-Board-Stats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\Boards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DAE2BC-FCC7-4E01-BEE4-086A357E3E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3530CC7B-F099-4EC9-909D-6EBF080C014B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Board Stats" sheetId="2" r:id="rId1"/>
@@ -1769,25 +1769,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
   <dimension ref="A1:L194"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="F1" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>317</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
@@ -1857,11 +1857,11 @@
         <v>1</v>
       </c>
       <c r="L3" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C3),E3)</f>
+        <f t="shared" ref="L3:L34" si="0">HYPERLINK(_xlfn.CONCAT($F$1,C3),E3)</f>
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2</v>
       </c>
@@ -1893,11 +1893,11 @@
         <v>2</v>
       </c>
       <c r="L4" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C4),E4)</f>
+        <f t="shared" si="0"/>
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1929,11 +1929,11 @@
         <v>2</v>
       </c>
       <c r="L5" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C5),E5)</f>
+        <f t="shared" si="0"/>
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1965,11 +1965,11 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C6),E6)</f>
+        <f t="shared" si="0"/>
         <v>Fire Storm Wood V2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>5</v>
       </c>
@@ -2001,11 +2001,11 @@
         <v>3</v>
       </c>
       <c r="L7" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C7),E7)</f>
+        <f t="shared" si="0"/>
         <v>Firemove Ltd V2 102</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6</v>
       </c>
@@ -2037,11 +2037,11 @@
         <v>4</v>
       </c>
       <c r="L8" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C8),E8)</f>
+        <f t="shared" si="0"/>
         <v>Firemove Ltd V2 112</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>7</v>
       </c>
@@ -2073,11 +2073,11 @@
         <v>2</v>
       </c>
       <c r="L9" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C9),E9)</f>
+        <f t="shared" si="0"/>
         <v>Firemove Ltd V2 122</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>8</v>
       </c>
@@ -2109,11 +2109,11 @@
         <v>2</v>
       </c>
       <c r="L10" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C10),E10)</f>
+        <f t="shared" si="0"/>
         <v>Firemove Ltd V2 130</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>9</v>
       </c>
@@ -2145,11 +2145,11 @@
         <v>5</v>
       </c>
       <c r="L11" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C11),E11)</f>
+        <f t="shared" si="0"/>
         <v>Firemove Ltd V2 140</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>10</v>
       </c>
@@ -2181,11 +2181,11 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C12),E12)</f>
+        <f t="shared" si="0"/>
         <v>Firemove V2 Wood</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>11</v>
       </c>
@@ -2214,11 +2214,11 @@
         <v>2</v>
       </c>
       <c r="L13" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C13),E13)</f>
+        <f t="shared" si="0"/>
         <v>firestorm 111</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>12</v>
       </c>
@@ -2250,11 +2250,11 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C14),E14)</f>
+        <f t="shared" si="0"/>
         <v>Firestorm LTD</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>13</v>
       </c>
@@ -2286,11 +2286,11 @@
         <v>1</v>
       </c>
       <c r="L15" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C15),E15)</f>
+        <f t="shared" si="0"/>
         <v>Firestorm LTD V2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>14</v>
       </c>
@@ -2322,11 +2322,11 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C16),E16)</f>
+        <f t="shared" si="0"/>
         <v>Firewave LTD</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>15</v>
       </c>
@@ -2355,11 +2355,11 @@
         <v>1</v>
       </c>
       <c r="L17" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C17),E17)</f>
+        <f t="shared" si="0"/>
         <v>freerace</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>16</v>
       </c>
@@ -2388,11 +2388,11 @@
         <v>5</v>
       </c>
       <c r="L18" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C18),E18)</f>
+        <f t="shared" si="0"/>
         <v>proto Firestorm V3 #053</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>17</v>
       </c>
@@ -2424,11 +2424,11 @@
         <v>1</v>
       </c>
       <c r="L19" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C19),E19)</f>
+        <f t="shared" si="0"/>
         <v>Proto X-Fire 98 V7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>18</v>
       </c>
@@ -2457,11 +2457,11 @@
         <v>5</v>
       </c>
       <c r="L20" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C20),E20)</f>
+        <f t="shared" si="0"/>
         <v>Slalom</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>19</v>
       </c>
@@ -2490,11 +2490,11 @@
         <v>4</v>
       </c>
       <c r="L21" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C21),E21)</f>
+        <f t="shared" si="0"/>
         <v>Slalom Large Proto</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>20</v>
       </c>
@@ -2526,11 +2526,11 @@
         <v>2</v>
       </c>
       <c r="L22" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C22),E22)</f>
+        <f t="shared" si="0"/>
         <v>Speed 41</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>21</v>
       </c>
@@ -2562,11 +2562,11 @@
         <v>3</v>
       </c>
       <c r="L23" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C23),E23)</f>
+        <f t="shared" si="0"/>
         <v>Speed 43</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>22</v>
       </c>
@@ -2598,11 +2598,11 @@
         <v>1</v>
       </c>
       <c r="L24" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C24),E24)</f>
+        <f t="shared" si="0"/>
         <v>speed board</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>23</v>
       </c>
@@ -2634,11 +2634,11 @@
         <v>2</v>
       </c>
       <c r="L25" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C25),E25)</f>
+        <f t="shared" si="0"/>
         <v>x fire</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>24</v>
       </c>
@@ -2670,11 +2670,11 @@
         <v>17</v>
       </c>
       <c r="L26" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C26),E26)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V6 105</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>25</v>
       </c>
@@ -2706,11 +2706,11 @@
         <v>24</v>
       </c>
       <c r="L27" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C27),E27)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V6 114</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>26</v>
       </c>
@@ -2742,11 +2742,11 @@
         <v>15</v>
       </c>
       <c r="L28" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C28),E28)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V6 122</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>27</v>
       </c>
@@ -2778,11 +2778,11 @@
         <v>5</v>
       </c>
       <c r="L29" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C29),E29)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V6 129</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>319</v>
       </c>
@@ -2817,11 +2817,11 @@
         <v>13</v>
       </c>
       <c r="L30" s="11" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C30),E30)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V6 90</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>29</v>
       </c>
@@ -2853,11 +2853,11 @@
         <v>18</v>
       </c>
       <c r="L31" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C31),E31)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V6 98</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>30</v>
       </c>
@@ -2889,11 +2889,11 @@
         <v>4</v>
       </c>
       <c r="L32" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C32),E32)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V7 105</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>31</v>
       </c>
@@ -2925,11 +2925,11 @@
         <v>4</v>
       </c>
       <c r="L33" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C33),E33)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V7 114</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>32</v>
       </c>
@@ -2961,11 +2961,11 @@
         <v>3</v>
       </c>
       <c r="L34" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C34),E34)</f>
+        <f t="shared" si="0"/>
         <v>X-Fire LTD V7 122</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>33</v>
       </c>
@@ -2997,11 +2997,11 @@
         <v>1</v>
       </c>
       <c r="L35" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C35),E35)</f>
+        <f t="shared" ref="L35:L66" si="1">HYPERLINK(_xlfn.CONCAT($F$1,C35),E35)</f>
         <v>X-Fire LTD V7 129</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>34</v>
       </c>
@@ -3033,11 +3033,11 @@
         <v>1</v>
       </c>
       <c r="L36" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C36),E36)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V7 80</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>35</v>
       </c>
@@ -3069,11 +3069,11 @@
         <v>1</v>
       </c>
       <c r="L37" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C37),E37)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V7 90</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>36</v>
       </c>
@@ -3105,11 +3105,11 @@
         <v>3</v>
       </c>
       <c r="L38" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C38),E38)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V7 98</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>37</v>
       </c>
@@ -3141,11 +3141,11 @@
         <v>1</v>
       </c>
       <c r="L39" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C39),E39)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire V5 LTD 128</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>320</v>
       </c>
@@ -3180,11 +3180,11 @@
         <v>3</v>
       </c>
       <c r="L40" s="10" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C40),E40)</f>
+        <f t="shared" si="1"/>
         <v>XiFire LTD V6 90</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>39</v>
       </c>
@@ -3216,11 +3216,11 @@
         <v>2</v>
       </c>
       <c r="L41" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C41),E41)</f>
+        <f t="shared" si="1"/>
         <v>Custom Speed</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>40</v>
       </c>
@@ -3252,11 +3252,11 @@
         <v>1</v>
       </c>
       <c r="L42" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C42),E42)</f>
+        <f t="shared" si="1"/>
         <v>Firemove</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>41</v>
       </c>
@@ -3282,11 +3282,11 @@
         <v>58</v>
       </c>
       <c r="L43" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C43),E43)</f>
+        <f t="shared" si="1"/>
         <v>firemove</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="15"/>
       <c r="B44">
         <v>42</v>
@@ -3319,11 +3319,11 @@
         <v>2</v>
       </c>
       <c r="L44" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C44),E44)</f>
+        <f t="shared" si="1"/>
         <v>FireMove 120 LTD</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>43</v>
       </c>
@@ -3355,11 +3355,11 @@
         <v>2</v>
       </c>
       <c r="L45" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C45),E45)</f>
+        <f t="shared" si="1"/>
         <v>FireMove 140 LTD</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>44</v>
       </c>
@@ -3391,11 +3391,11 @@
         <v>1</v>
       </c>
       <c r="L46" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C46),E46)</f>
+        <f t="shared" si="1"/>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>45</v>
       </c>
@@ -3427,11 +3427,11 @@
         <v>2</v>
       </c>
       <c r="L47" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C47),E47)</f>
+        <f t="shared" si="1"/>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>46</v>
       </c>
@@ -3463,11 +3463,11 @@
         <v>1</v>
       </c>
       <c r="L48" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C48),E48)</f>
+        <f t="shared" si="1"/>
         <v>Firemove LTD 130</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>47</v>
       </c>
@@ -3499,11 +3499,11 @@
         <v>2</v>
       </c>
       <c r="L49" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C49),E49)</f>
+        <f t="shared" si="1"/>
         <v>firerace</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>48</v>
       </c>
@@ -3535,11 +3535,11 @@
         <v>1</v>
       </c>
       <c r="L50" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C50),E50)</f>
+        <f t="shared" si="1"/>
         <v>Firerace W-tech 102</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>49</v>
       </c>
@@ -3571,11 +3571,11 @@
         <v>1</v>
       </c>
       <c r="L51" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C51),E51)</f>
+        <f t="shared" si="1"/>
         <v>Firerace W-tech 112</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>50</v>
       </c>
@@ -3607,11 +3607,11 @@
         <v>1</v>
       </c>
       <c r="L52" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C52),E52)</f>
+        <f t="shared" si="1"/>
         <v>Firestorm 120 W-tech</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>51</v>
       </c>
@@ -3640,11 +3640,11 @@
         <v>1</v>
       </c>
       <c r="L53" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C53),E53)</f>
+        <f t="shared" si="1"/>
         <v>FireWave 102 LTD</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54">
         <v>52</v>
@@ -3677,11 +3677,11 @@
         <v>1</v>
       </c>
       <c r="L54" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C54),E54)</f>
+        <f t="shared" si="1"/>
         <v>Freestyle Wave</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>53</v>
       </c>
@@ -3713,11 +3713,11 @@
         <v>4</v>
       </c>
       <c r="L55" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C55),E55)</f>
+        <f t="shared" si="1"/>
         <v>Freestyle Wave LTD</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>54</v>
       </c>
@@ -3749,11 +3749,11 @@
         <v>1</v>
       </c>
       <c r="L56" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C56),E56)</f>
+        <f t="shared" si="1"/>
         <v>Freestyle Wave LTD</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>55</v>
       </c>
@@ -3782,11 +3782,11 @@
         <v>2</v>
       </c>
       <c r="L57" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C57),E57)</f>
+        <f t="shared" si="1"/>
         <v>FreeStyleWave</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>56</v>
       </c>
@@ -3818,11 +3818,11 @@
         <v>2</v>
       </c>
       <c r="L58" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C58),E58)</f>
+        <f t="shared" si="1"/>
         <v>Frrestyle Wave 102</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>57</v>
       </c>
@@ -3848,11 +3848,11 @@
         <v>58</v>
       </c>
       <c r="L59" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C59),E59)</f>
+        <f t="shared" si="1"/>
         <v>Slalom</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>58</v>
       </c>
@@ -3884,11 +3884,11 @@
         <v>2</v>
       </c>
       <c r="L60" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C60),E60)</f>
+        <f t="shared" si="1"/>
         <v>Slalom/speed</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>59</v>
       </c>
@@ -3920,11 +3920,11 @@
         <v>1</v>
       </c>
       <c r="L61" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C61),E61)</f>
+        <f t="shared" si="1"/>
         <v>X-fire LTD V5</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>60</v>
       </c>
@@ -3956,11 +3956,11 @@
         <v>11</v>
       </c>
       <c r="L62" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C62),E62)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V5 105</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>61</v>
       </c>
@@ -3992,11 +3992,11 @@
         <v>15</v>
       </c>
       <c r="L63" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C63),E63)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V5 114</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>62</v>
       </c>
@@ -4028,11 +4028,11 @@
         <v>9</v>
       </c>
       <c r="L64" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C64),E64)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V5 114 2013</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>63</v>
       </c>
@@ -4064,11 +4064,11 @@
         <v>10</v>
       </c>
       <c r="L65" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C65),E65)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V5 122</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>64</v>
       </c>
@@ -4100,11 +4100,11 @@
         <v>14</v>
       </c>
       <c r="L66" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C66),E66)</f>
+        <f t="shared" si="1"/>
         <v>X-Fire LTD V5 129</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>65</v>
       </c>
@@ -4136,11 +4136,11 @@
         <v>7</v>
       </c>
       <c r="L67" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C67),E67)</f>
+        <f t="shared" ref="L67:L98" si="2">HYPERLINK(_xlfn.CONCAT($F$1,C67),E67)</f>
         <v>X-Fire LTD V5 90</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>66</v>
       </c>
@@ -4172,11 +4172,11 @@
         <v>24</v>
       </c>
       <c r="L68" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C68),E68)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire LTD V5 98</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>67</v>
       </c>
@@ -4208,11 +4208,11 @@
         <v>3</v>
       </c>
       <c r="L69" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C69),E69)</f>
+        <f t="shared" si="2"/>
         <v>Custom Speed</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>68</v>
       </c>
@@ -4244,11 +4244,11 @@
         <v>2</v>
       </c>
       <c r="L70" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C70),E70)</f>
+        <f t="shared" si="2"/>
         <v>Fire Storm 111</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>69</v>
       </c>
@@ -4280,11 +4280,11 @@
         <v>3</v>
       </c>
       <c r="L71" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C71),E71)</f>
+        <f t="shared" si="2"/>
         <v>Fire Storm 138 W-Tech</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>70</v>
       </c>
@@ -4316,11 +4316,11 @@
         <v>3</v>
       </c>
       <c r="L72" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C72),E72)</f>
+        <f t="shared" si="2"/>
         <v>Fire Strom LTD</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>71</v>
       </c>
@@ -4352,11 +4352,11 @@
         <v>1</v>
       </c>
       <c r="L73" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C73),E73)</f>
+        <f t="shared" si="2"/>
         <v>firemove 100</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>72</v>
       </c>
@@ -4388,11 +4388,11 @@
         <v>2</v>
       </c>
       <c r="L74" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C74),E74)</f>
+        <f t="shared" si="2"/>
         <v>FireMove 100 X-Tech</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>73</v>
       </c>
@@ -4424,11 +4424,11 @@
         <v>1</v>
       </c>
       <c r="L75" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C75),E75)</f>
+        <f t="shared" si="2"/>
         <v>firemove 110</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>74</v>
       </c>
@@ -4460,11 +4460,11 @@
         <v>1</v>
       </c>
       <c r="L76" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C76),E76)</f>
+        <f t="shared" si="2"/>
         <v>FireMove 110 X-Tech</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>75</v>
       </c>
@@ -4496,11 +4496,11 @@
         <v>1</v>
       </c>
       <c r="L77" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C77),E77)</f>
+        <f t="shared" si="2"/>
         <v>Firemove 120</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>76</v>
       </c>
@@ -4532,11 +4532,11 @@
         <v>1</v>
       </c>
       <c r="L78" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C78),E78)</f>
+        <f t="shared" si="2"/>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>77</v>
       </c>
@@ -4568,11 +4568,11 @@
         <v>1</v>
       </c>
       <c r="L79" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C79),E79)</f>
+        <f t="shared" si="2"/>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>78</v>
       </c>
@@ -4604,11 +4604,11 @@
         <v>2</v>
       </c>
       <c r="L80" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C80),E80)</f>
+        <f t="shared" si="2"/>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>79</v>
       </c>
@@ -4640,11 +4640,11 @@
         <v>4</v>
       </c>
       <c r="L81" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C81),E81)</f>
+        <f t="shared" si="2"/>
         <v>Firemove LTD 100</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>80</v>
       </c>
@@ -4676,11 +4676,11 @@
         <v>6</v>
       </c>
       <c r="L82" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C82),E82)</f>
+        <f t="shared" si="2"/>
         <v>Firemove LTD 110</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>81</v>
       </c>
@@ -4712,11 +4712,11 @@
         <v>1</v>
       </c>
       <c r="L83" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C83),E83)</f>
+        <f t="shared" si="2"/>
         <v>Firerace V3 122</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>82</v>
       </c>
@@ -4748,11 +4748,11 @@
         <v>3</v>
       </c>
       <c r="L84" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C84),E84)</f>
+        <f t="shared" si="2"/>
         <v>Firestorm</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>83</v>
       </c>
@@ -4784,11 +4784,11 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C85),E85)</f>
+        <f t="shared" si="2"/>
         <v>Freestyle Wave</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>84</v>
       </c>
@@ -4820,11 +4820,11 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C86),E86)</f>
+        <f t="shared" si="2"/>
         <v>Freestyle Wave 90 X-Tech</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>85</v>
       </c>
@@ -4856,11 +4856,11 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C87),E87)</f>
+        <f t="shared" si="2"/>
         <v>Freestyle Wave 96 LTD</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>86</v>
       </c>
@@ -4892,11 +4892,11 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C88),E88)</f>
+        <f t="shared" si="2"/>
         <v>FreestyleWave</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B89">
         <v>87</v>
       </c>
@@ -4928,11 +4928,11 @@
         <v>3</v>
       </c>
       <c r="L89" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C89),E89)</f>
+        <f t="shared" si="2"/>
         <v>TwinTip LTD</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B90">
         <v>88</v>
       </c>
@@ -4964,11 +4964,11 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C90),E90)</f>
+        <f t="shared" si="2"/>
         <v>wave cult</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91">
         <v>89</v>
       </c>
@@ -4994,11 +4994,11 @@
         <v>58</v>
       </c>
       <c r="L91" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C91),E91)</f>
+        <f t="shared" si="2"/>
         <v>X-fire</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92">
         <v>90</v>
       </c>
@@ -5027,11 +5027,11 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C92),E92)</f>
+        <f t="shared" si="2"/>
         <v>xfire 105</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>91</v>
       </c>
@@ -5063,11 +5063,11 @@
         <v>3</v>
       </c>
       <c r="L93" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C93),E93)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire 80 V</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B94">
         <v>92</v>
       </c>
@@ -5096,11 +5096,11 @@
         <v>5</v>
       </c>
       <c r="L94" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C94),E94)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire LTD 105</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B95">
         <v>93</v>
       </c>
@@ -5132,11 +5132,11 @@
         <v>8</v>
       </c>
       <c r="L95" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C95),E95)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire Ltd V3 122</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B96">
         <v>94</v>
       </c>
@@ -5168,11 +5168,11 @@
         <v>3</v>
       </c>
       <c r="L96" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C96),E96)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire LTD V4</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97">
         <v>95</v>
       </c>
@@ -5204,11 +5204,11 @@
         <v>5</v>
       </c>
       <c r="L97" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C97),E97)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire LTD V4 105</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98">
         <v>96</v>
       </c>
@@ -5240,11 +5240,11 @@
         <v>22</v>
       </c>
       <c r="L98" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C98),E98)</f>
+        <f t="shared" si="2"/>
         <v>X-Fire LTD V4 114</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99">
         <v>97</v>
       </c>
@@ -5276,11 +5276,11 @@
         <v>11</v>
       </c>
       <c r="L99" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C99),E99)</f>
+        <f t="shared" ref="L99:L130" si="3">HYPERLINK(_xlfn.CONCAT($F$1,C99),E99)</f>
         <v>X-Fire LTD V4 122</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100">
         <v>98</v>
       </c>
@@ -5312,11 +5312,11 @@
         <v>9</v>
       </c>
       <c r="L100" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C100),E100)</f>
+        <f t="shared" si="3"/>
         <v>X-Fire LTD V4 129</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101">
         <v>99</v>
       </c>
@@ -5348,11 +5348,11 @@
         <v>8</v>
       </c>
       <c r="L101" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C101),E101)</f>
+        <f t="shared" si="3"/>
         <v>X-Fire LTD V4 90</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102">
         <v>100</v>
       </c>
@@ -5384,11 +5384,11 @@
         <v>15</v>
       </c>
       <c r="L102" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C102),E102)</f>
+        <f t="shared" si="3"/>
         <v>X-Fire LTD V4 98</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B103">
         <v>101</v>
       </c>
@@ -5420,11 +5420,11 @@
         <v>8</v>
       </c>
       <c r="L103" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C103),E103)</f>
+        <f t="shared" si="3"/>
         <v>X-FIRE V3</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B104">
         <v>102</v>
       </c>
@@ -5456,11 +5456,11 @@
         <v>1</v>
       </c>
       <c r="L104" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C104),E104)</f>
+        <f t="shared" si="3"/>
         <v>X-Fire V4</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B105">
         <v>103</v>
       </c>
@@ -5489,11 +5489,11 @@
         <v>13</v>
       </c>
       <c r="L105" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C105),E105)</f>
+        <f t="shared" si="3"/>
         <v>Atom IQ</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B106">
         <v>104</v>
       </c>
@@ -5525,11 +5525,11 @@
         <v>1</v>
       </c>
       <c r="L106" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C106),E106)</f>
+        <f t="shared" si="3"/>
         <v>Atom IQ 100 Tufskin</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B107">
         <v>105</v>
       </c>
@@ -5561,11 +5561,11 @@
         <v>4</v>
       </c>
       <c r="L107" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C107),E107)</f>
+        <f t="shared" si="3"/>
         <v>Atom IQ carbon 110</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B108">
         <v>106</v>
       </c>
@@ -5597,11 +5597,11 @@
         <v>6</v>
       </c>
       <c r="L108" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C108),E108)</f>
+        <f t="shared" si="3"/>
         <v>AtomIQ 120 Carbon</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B109">
         <v>107</v>
       </c>
@@ -5633,11 +5633,11 @@
         <v>1</v>
       </c>
       <c r="L109" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C109),E109)</f>
+        <f t="shared" si="3"/>
         <v>Carve 111 wood</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B110">
         <v>108</v>
       </c>
@@ -5669,11 +5669,11 @@
         <v>2</v>
       </c>
       <c r="L110" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C110),E110)</f>
+        <f t="shared" si="3"/>
         <v>Fórmula 167 blue</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B111">
         <v>109</v>
       </c>
@@ -5705,11 +5705,11 @@
         <v>3</v>
       </c>
       <c r="L111" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C111),E111)</f>
+        <f t="shared" si="3"/>
         <v>Futura</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B112">
         <v>110</v>
       </c>
@@ -5741,11 +5741,11 @@
         <v>2</v>
       </c>
       <c r="L112" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C112),E112)</f>
+        <f t="shared" si="3"/>
         <v>Futura 104 carbon</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B113">
         <v>111</v>
       </c>
@@ -5777,11 +5777,11 @@
         <v>2</v>
       </c>
       <c r="L113" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C113),E113)</f>
+        <f t="shared" si="3"/>
         <v>Futura 104 wood</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B114">
         <v>112</v>
       </c>
@@ -5813,11 +5813,11 @@
         <v>2</v>
       </c>
       <c r="L114" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C114),E114)</f>
+        <f t="shared" si="3"/>
         <v>Futura 114 carbon</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115">
         <v>113</v>
       </c>
@@ -5849,11 +5849,11 @@
         <v>8</v>
       </c>
       <c r="L115" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C115),E115)</f>
+        <f t="shared" si="3"/>
         <v>Futura 114 wood</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116">
         <v>114</v>
       </c>
@@ -5885,11 +5885,11 @@
         <v>4</v>
       </c>
       <c r="L116" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C116),E116)</f>
+        <f t="shared" si="3"/>
         <v>Futura 124 Carbon</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>115</v>
       </c>
@@ -5921,11 +5921,11 @@
         <v>5</v>
       </c>
       <c r="L117" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C117),E117)</f>
+        <f t="shared" si="3"/>
         <v>Futura 124 Wood</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B118">
         <v>116</v>
       </c>
@@ -5957,11 +5957,11 @@
         <v>1</v>
       </c>
       <c r="L118" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C118),E118)</f>
+        <f t="shared" si="3"/>
         <v>Futura 133 Wood</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B119">
         <v>117</v>
       </c>
@@ -5993,11 +5993,11 @@
         <v>3</v>
       </c>
       <c r="L119" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C119),E119)</f>
+        <f t="shared" si="3"/>
         <v>Futura 134 Carbon</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B120">
         <v>118</v>
       </c>
@@ -6029,11 +6029,11 @@
         <v>5</v>
       </c>
       <c r="L120" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C120),E120)</f>
+        <f t="shared" si="3"/>
         <v>Futura 134 Wood</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B121">
         <v>119</v>
       </c>
@@ -6065,11 +6065,11 @@
         <v>3</v>
       </c>
       <c r="L121" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C121),E121)</f>
+        <f t="shared" si="3"/>
         <v>Futura 90 Wood</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B122">
         <v>120</v>
       </c>
@@ -6101,11 +6101,11 @@
         <v>1</v>
       </c>
       <c r="L122" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C122),E122)</f>
+        <f t="shared" si="3"/>
         <v>Futura 93 wood</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B123">
         <v>121</v>
       </c>
@@ -6137,11 +6137,11 @@
         <v>1</v>
       </c>
       <c r="L123" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C123),E123)</f>
+        <f t="shared" si="3"/>
         <v>Futura 97 wood</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B124">
         <v>122</v>
       </c>
@@ -6173,11 +6173,11 @@
         <v>1</v>
       </c>
       <c r="L124" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C124),E124)</f>
+        <f t="shared" si="3"/>
         <v>Futura carbon</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B125">
         <v>123</v>
       </c>
@@ -6206,11 +6206,11 @@
         <v>2</v>
       </c>
       <c r="L125" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C125),E125)</f>
+        <f t="shared" si="3"/>
         <v>Futura Carbon</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B126">
         <v>124</v>
       </c>
@@ -6242,11 +6242,11 @@
         <v>2</v>
       </c>
       <c r="L126" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C126),E126)</f>
+        <f t="shared" si="3"/>
         <v>Go 139 Tufskin</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B127">
         <v>125</v>
       </c>
@@ -6278,11 +6278,11 @@
         <v>6</v>
       </c>
       <c r="L127" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C127),E127)</f>
+        <f t="shared" si="3"/>
         <v>Isonic</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B128">
         <v>126</v>
       </c>
@@ -6314,11 +6314,11 @@
         <v>56</v>
       </c>
       <c r="L128" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C128),E128)</f>
+        <f t="shared" si="3"/>
         <v>iSonic 107 Carbon</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B129">
         <v>127</v>
       </c>
@@ -6350,11 +6350,11 @@
         <v>1</v>
       </c>
       <c r="L129" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C129),E129)</f>
+        <f t="shared" si="3"/>
         <v>iSonic 107 wood</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>128</v>
       </c>
@@ -6386,11 +6386,11 @@
         <v>17</v>
       </c>
       <c r="L130" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C130),E130)</f>
+        <f t="shared" si="3"/>
         <v>iSonic 110 Carbon</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B131">
         <v>129</v>
       </c>
@@ -6422,11 +6422,11 @@
         <v>4</v>
       </c>
       <c r="L131" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C131),E131)</f>
+        <f t="shared" ref="L131:L162" si="4">HYPERLINK(_xlfn.CONCAT($F$1,C131),E131)</f>
         <v>Isonic 117</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>130</v>
       </c>
@@ -6458,11 +6458,11 @@
         <v>1</v>
       </c>
       <c r="L132" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C132),E132)</f>
+        <f t="shared" si="4"/>
         <v>iSonic 117 wood</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B133">
         <v>131</v>
       </c>
@@ -6494,11 +6494,11 @@
         <v>18</v>
       </c>
       <c r="L133" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C133),E133)</f>
+        <f t="shared" si="4"/>
         <v>Isonic 120 carbon</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B134">
         <v>132</v>
       </c>
@@ -6530,11 +6530,11 @@
         <v>18</v>
       </c>
       <c r="L134" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C134),E134)</f>
+        <f t="shared" si="4"/>
         <v>iSonic 130 Carbon</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B135">
         <v>133</v>
       </c>
@@ -6566,11 +6566,11 @@
         <v>2</v>
       </c>
       <c r="L135" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C135),E135)</f>
+        <f t="shared" si="4"/>
         <v>Isonic 80 Wood</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B136">
         <v>134</v>
       </c>
@@ -6602,11 +6602,11 @@
         <v>23</v>
       </c>
       <c r="L136" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C136),E136)</f>
+        <f t="shared" si="4"/>
         <v>isonic 87 Carbon</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B137">
         <v>135</v>
       </c>
@@ -6638,11 +6638,11 @@
         <v>3</v>
       </c>
       <c r="L137" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C137),E137)</f>
+        <f t="shared" si="4"/>
         <v>iSonic 87 wood</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B138">
         <v>136</v>
       </c>
@@ -6674,11 +6674,11 @@
         <v>27</v>
       </c>
       <c r="L138" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C138),E138)</f>
+        <f t="shared" si="4"/>
         <v>Isonic 90 Carbon</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B139">
         <v>137</v>
       </c>
@@ -6710,11 +6710,11 @@
         <v>22</v>
       </c>
       <c r="L139" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C139),E139)</f>
+        <f t="shared" si="4"/>
         <v>iSonic 97 Carbon</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B140">
         <v>138</v>
       </c>
@@ -6746,11 +6746,11 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C140),E140)</f>
+        <f t="shared" si="4"/>
         <v>Isonic 97 wood</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B141">
         <v>139</v>
       </c>
@@ -6782,11 +6782,11 @@
         <v>4</v>
       </c>
       <c r="L141" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C141),E141)</f>
+        <f t="shared" si="4"/>
         <v>Isonic carbon</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
         <v>318</v>
       </c>
@@ -6821,11 +6821,11 @@
         <v>4</v>
       </c>
       <c r="L142" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C142),E142)</f>
+        <f t="shared" si="4"/>
         <v>I-Sonic Speed 54</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B143">
         <v>141</v>
       </c>
@@ -6857,11 +6857,11 @@
         <v>8</v>
       </c>
       <c r="L143" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C143),E143)</f>
+        <f t="shared" si="4"/>
         <v>iSonic speed special w44</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B144">
         <v>142</v>
       </c>
@@ -6893,11 +6893,11 @@
         <v>9</v>
       </c>
       <c r="L144" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C144),E144)</f>
+        <f t="shared" si="4"/>
         <v>Isonic speed special W49</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B145">
         <v>143</v>
       </c>
@@ -6929,11 +6929,11 @@
         <v>7</v>
       </c>
       <c r="L145" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C145),E145)</f>
+        <f t="shared" si="4"/>
         <v>iSonic Speed Special W54</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146">
         <v>144</v>
       </c>
@@ -6962,11 +6962,11 @@
         <v>2</v>
       </c>
       <c r="L146" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C146),E146)</f>
+        <f t="shared" si="4"/>
         <v>iSonics carbon</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147">
         <v>145</v>
       </c>
@@ -6995,11 +6995,11 @@
         <v>4</v>
       </c>
       <c r="L147" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C147),E147)</f>
+        <f t="shared" si="4"/>
         <v>Kode 87 Wood Carbon</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148">
         <v>146</v>
       </c>
@@ -7031,11 +7031,11 @@
         <v>4</v>
       </c>
       <c r="L148" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C148),E148)</f>
+        <f t="shared" si="4"/>
         <v>Kode FreeWave Wood</v>
       </c>
     </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149">
         <v>147</v>
       </c>
@@ -7061,11 +7061,11 @@
         <v>22</v>
       </c>
       <c r="L149" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C149),E149)</f>
+        <f t="shared" si="4"/>
         <v>No idea</v>
       </c>
     </row>
-    <row r="150" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B150">
         <v>148</v>
       </c>
@@ -7097,11 +7097,11 @@
         <v>4</v>
       </c>
       <c r="L150" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C150),E150)</f>
+        <f t="shared" si="4"/>
         <v>Slalom One</v>
       </c>
     </row>
-    <row r="151" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B151">
         <v>149</v>
       </c>
@@ -7133,11 +7133,11 @@
         <v>1</v>
       </c>
       <c r="L151" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C151),E151)</f>
+        <f t="shared" si="4"/>
         <v>Speed special 58</v>
       </c>
     </row>
-    <row r="152" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B152">
         <v>150</v>
       </c>
@@ -7169,11 +7169,11 @@
         <v>2</v>
       </c>
       <c r="L152" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C152),E152)</f>
+        <f t="shared" si="4"/>
         <v>Starboard AtomIQ 140</v>
       </c>
     </row>
-    <row r="153" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B153">
         <v>151</v>
       </c>
@@ -7205,11 +7205,11 @@
         <v>2</v>
       </c>
       <c r="L153" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C153),E153)</f>
+        <f t="shared" si="4"/>
         <v>Ultrasonic Wood</v>
       </c>
     </row>
-    <row r="154" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B154">
         <v>152</v>
       </c>
@@ -7241,11 +7241,11 @@
         <v>1</v>
       </c>
       <c r="L154" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C154),E154)</f>
+        <f t="shared" si="4"/>
         <v>Windsup Touring Delux Inflatable</v>
       </c>
     </row>
-    <row r="155" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B155">
         <v>153</v>
       </c>
@@ -7277,11 +7277,11 @@
         <v>2</v>
       </c>
       <c r="L155" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C155),E155)</f>
+        <f t="shared" si="4"/>
         <v>AllWave</v>
       </c>
     </row>
-    <row r="156" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B156">
         <v>154</v>
       </c>
@@ -7310,11 +7310,11 @@
         <v>3</v>
       </c>
       <c r="L156" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C156),E156)</f>
+        <f t="shared" si="4"/>
         <v>Eagle</v>
       </c>
     </row>
-    <row r="157" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B157">
         <v>155</v>
       </c>
@@ -7346,11 +7346,11 @@
         <v>5</v>
       </c>
       <c r="L157" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C157),E157)</f>
+        <f t="shared" si="4"/>
         <v>Eagle 100</v>
       </c>
     </row>
-    <row r="158" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B158">
         <v>156</v>
       </c>
@@ -7382,11 +7382,11 @@
         <v>5</v>
       </c>
       <c r="L158" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C158),E158)</f>
+        <f t="shared" si="4"/>
         <v>Eagle 126</v>
       </c>
     </row>
-    <row r="159" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B159">
         <v>157</v>
       </c>
@@ -7418,11 +7418,11 @@
         <v>9</v>
       </c>
       <c r="L159" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C159),E159)</f>
+        <f t="shared" si="4"/>
         <v>Falcon</v>
       </c>
     </row>
-    <row r="160" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B160">
         <v>158</v>
       </c>
@@ -7454,11 +7454,11 @@
         <v>30</v>
       </c>
       <c r="L160" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C160),E160)</f>
+        <f t="shared" si="4"/>
         <v>Falcon 105</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B161">
         <v>159</v>
       </c>
@@ -7490,11 +7490,11 @@
         <v>27</v>
       </c>
       <c r="L161" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C161),E161)</f>
+        <f t="shared" si="4"/>
         <v>Falcon 125</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B162">
         <v>160</v>
       </c>
@@ -7526,11 +7526,11 @@
         <v>5</v>
       </c>
       <c r="L162" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C162),E162)</f>
+        <f t="shared" si="4"/>
         <v>Falcon 145</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B163">
         <v>161</v>
       </c>
@@ -7562,11 +7562,11 @@
         <v>61</v>
       </c>
       <c r="L163" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C163),E163)</f>
+        <f t="shared" ref="L163:L194" si="5">HYPERLINK(_xlfn.CONCAT($F$1,C163),E163)</f>
         <v>Falcon 90</v>
       </c>
     </row>
-    <row r="164" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B164">
         <v>162</v>
       </c>
@@ -7598,11 +7598,11 @@
         <v>1</v>
       </c>
       <c r="L164" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C164),E164)</f>
+        <f t="shared" si="5"/>
         <v>Falcon 90 Proto</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B165">
         <v>163</v>
       </c>
@@ -7634,11 +7634,11 @@
         <v>8</v>
       </c>
       <c r="L165" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C165),E165)</f>
+        <f t="shared" si="5"/>
         <v>Falcon Formula TT</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B166">
         <v>164</v>
       </c>
@@ -7670,11 +7670,11 @@
         <v>1</v>
       </c>
       <c r="L166" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C166),E166)</f>
+        <f t="shared" si="5"/>
         <v>Falcon prototype</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B167">
         <v>165</v>
       </c>
@@ -7706,11 +7706,11 @@
         <v>3</v>
       </c>
       <c r="L167" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C167),E167)</f>
+        <f t="shared" si="5"/>
         <v>Falcon SL 105</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B168">
         <v>166</v>
       </c>
@@ -7742,11 +7742,11 @@
         <v>3</v>
       </c>
       <c r="L168" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C168),E168)</f>
+        <f t="shared" si="5"/>
         <v>Falcon SL 145</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B169">
         <v>167</v>
       </c>
@@ -7778,11 +7778,11 @@
         <v>6</v>
       </c>
       <c r="L169" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C169),E169)</f>
+        <f t="shared" si="5"/>
         <v>Falcon SL90</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B170">
         <v>168</v>
       </c>
@@ -7814,11 +7814,11 @@
         <v>2</v>
       </c>
       <c r="L170" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C170),E170)</f>
+        <f t="shared" si="5"/>
         <v>Falcon Slalom 105</v>
       </c>
     </row>
-    <row r="171" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B171">
         <v>169</v>
       </c>
@@ -7847,11 +7847,11 @@
         <v>2</v>
       </c>
       <c r="L171" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C171),E171)</f>
+        <f t="shared" si="5"/>
         <v>Falcon Speed</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B172">
         <v>170</v>
       </c>
@@ -7883,11 +7883,11 @@
         <v>1</v>
       </c>
       <c r="L172" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C172),E172)</f>
+        <f t="shared" si="5"/>
         <v>Freemove</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B173">
         <v>171</v>
       </c>
@@ -7919,11 +7919,11 @@
         <v>2</v>
       </c>
       <c r="L173" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C173),E173)</f>
+        <f t="shared" si="5"/>
         <v>Freewave</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B174">
         <v>172</v>
       </c>
@@ -7955,11 +7955,11 @@
         <v>10</v>
       </c>
       <c r="L174" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C174),E174)</f>
+        <f t="shared" si="5"/>
         <v>Freewave 104</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B175">
         <v>173</v>
       </c>
@@ -7991,11 +7991,11 @@
         <v>5</v>
       </c>
       <c r="L175" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C175),E175)</f>
+        <f t="shared" si="5"/>
         <v>Freewave 86</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B176">
         <v>174</v>
       </c>
@@ -8027,11 +8027,11 @@
         <v>10</v>
       </c>
       <c r="L176" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C176),E176)</f>
+        <f t="shared" si="5"/>
         <v>Freewave 95</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B177">
         <v>175</v>
       </c>
@@ -8063,11 +8063,11 @@
         <v>11</v>
       </c>
       <c r="L177" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C177),E177)</f>
+        <f t="shared" si="5"/>
         <v>Hawk 108</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B178">
         <v>176</v>
       </c>
@@ -8099,11 +8099,11 @@
         <v>5</v>
       </c>
       <c r="L178" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C178),E178)</f>
+        <f t="shared" si="5"/>
         <v>Hawk 123</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B179">
         <v>177</v>
       </c>
@@ -8135,11 +8135,11 @@
         <v>6</v>
       </c>
       <c r="L179" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C179),E179)</f>
+        <f t="shared" si="5"/>
         <v>Shark</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B180">
         <v>178</v>
       </c>
@@ -8171,11 +8171,11 @@
         <v>9</v>
       </c>
       <c r="L180" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C180),E180)</f>
+        <f t="shared" si="5"/>
         <v>Shark 130 Ltd</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B181">
         <v>179</v>
       </c>
@@ -8207,11 +8207,11 @@
         <v>4</v>
       </c>
       <c r="L181" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C181),E181)</f>
+        <f t="shared" si="5"/>
         <v>Shark HRS 145 L</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
         <v>319</v>
       </c>
@@ -8246,11 +8246,11 @@
         <v>1</v>
       </c>
       <c r="L182" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C182),E182)</f>
+        <f t="shared" si="5"/>
         <v>Attitude Inspiro 79</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B183">
         <v>181</v>
       </c>
@@ -8279,11 +8279,11 @@
         <v>3</v>
       </c>
       <c r="L183" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C183),E183)</f>
+        <f t="shared" si="5"/>
         <v>Attitude Inspiro 87</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B184">
         <v>182</v>
       </c>
@@ -8315,11 +8315,11 @@
         <v>4</v>
       </c>
       <c r="L184" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C184),E184)</f>
+        <f t="shared" si="5"/>
         <v>Formula 98 N.T.</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B185">
         <v>183</v>
       </c>
@@ -8348,11 +8348,11 @@
         <v>4</v>
       </c>
       <c r="L185" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C185),E185)</f>
+        <f t="shared" si="5"/>
         <v>GT Special 54</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B186">
         <v>184</v>
       </c>
@@ -8384,11 +8384,11 @@
         <v>8</v>
       </c>
       <c r="L186" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C186),E186)</f>
+        <f t="shared" si="5"/>
         <v>GT Special 73</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B187">
         <v>185</v>
       </c>
@@ -8420,11 +8420,11 @@
         <v>2</v>
       </c>
       <c r="L187" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C187),E187)</f>
+        <f t="shared" si="5"/>
         <v>GT Special 86</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B188">
         <v>186</v>
       </c>
@@ -8453,11 +8453,11 @@
         <v>2</v>
       </c>
       <c r="L188" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C188),E188)</f>
+        <f t="shared" si="5"/>
         <v>Kauli Pro 81</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B189">
         <v>187</v>
       </c>
@@ -8489,11 +8489,11 @@
         <v>3</v>
       </c>
       <c r="L189" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C189),E189)</f>
+        <f t="shared" si="5"/>
         <v>Maxx Ride 104</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B190">
         <v>188</v>
       </c>
@@ -8522,11 +8522,11 @@
         <v>2</v>
       </c>
       <c r="L190" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C190),E190)</f>
+        <f t="shared" si="5"/>
         <v>Maxx Ride 92</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B191">
         <v>189</v>
       </c>
@@ -8558,11 +8558,11 @@
         <v>0</v>
       </c>
       <c r="L191" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C191),E191)</f>
+        <f t="shared" si="5"/>
         <v>Mx 57</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B192">
         <v>190</v>
       </c>
@@ -8594,11 +8594,11 @@
         <v>1</v>
       </c>
       <c r="L192" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C192),E192)</f>
+        <f t="shared" si="5"/>
         <v>Type F 64</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B193">
         <v>191</v>
       </c>
@@ -8630,11 +8630,11 @@
         <v>4</v>
       </c>
       <c r="L193" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C193),E193)</f>
+        <f t="shared" si="5"/>
         <v>Type F 75</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B194">
         <v>192</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="1" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT($F$1,C194),E194)</f>
+        <f t="shared" si="5"/>
         <v>Type F 85</v>
       </c>
     </row>
@@ -8684,11 +8684,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A702A5F9-18CA-47B5-B545-037F63A1FD14}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="8">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>198</v>
@@ -8700,7 +8700,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -8711,7 +8711,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>208</v>
       </c>
@@ -8720,10 +8720,10 @@
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" ref="D3:D13" si="0">HYPERLINK(_xlfn.CONCAT($B$1,$C3,"&amp;eqyear=",$A$1),_xlfn.CONCAT($A$1))</f>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>209</v>
       </c>
@@ -8732,10 +8732,10 @@
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>210</v>
       </c>
@@ -8744,10 +8744,10 @@
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>211</v>
       </c>
@@ -8756,10 +8756,10 @@
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>207</v>
       </c>
@@ -8768,10 +8768,10 @@
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>205</v>
       </c>
@@ -8780,10 +8780,10 @@
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>204</v>
       </c>
@@ -8792,10 +8792,10 @@
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>203</v>
       </c>
@@ -8804,10 +8804,10 @@
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>202</v>
       </c>
@@ -8816,10 +8816,10 @@
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>201</v>
       </c>
@@ -8828,10 +8828,10 @@
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>200</v>
       </c>
@@ -8840,10 +8840,10 @@
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
@@ -8852,10 +8852,10 @@
       </c>
       <c r="D14" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($B$1,$C14,"&amp;eqyear=",$A$1),_xlfn.CONCAT($A$1))</f>
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>212</v>
       </c>
@@ -8877,94 +8877,94 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467583F9-C105-4DC5-AB97-B32AA9231D3E}">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2001</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2002</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2003</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2004</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2005</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2006</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2007</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2008</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2009</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2010</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2011</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2012</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2013</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2014</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2015</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2016</v>
       </c>
